--- a/out/analysis_result.xlsx
+++ b/out/analysis_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\ВайбКодинг\Ai Coder\Programm Ai Coder\.aicoder\Projects\yandex-direct-analytic-datas-project\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFF6927-BD79-4008-B1C3-3092ADB8C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C61785-F63C-4502-9398-BCC9477709B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Обзор" sheetId="1" r:id="rId1"/>
@@ -8011,7 +8011,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$₽-419]"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8029,6 +8029,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8056,7 +8063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8067,6 +8074,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8692,7 +8702,7 @@
       <c r="B2" s="5" t="s">
         <v>2620</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -9714,7 +9724,7 @@
       <c r="B2" s="5" t="s">
         <v>2648</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
